--- a/优衣库订单统计表.xlsx
+++ b/优衣库订单统计表.xlsx
@@ -1026,7 +1026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O197"/>
+  <dimension ref="A1:O269"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="11.5" customWidth="1" style="1" min="1" max="1"/>
@@ -10303,375 +10303,4383 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
+      <c r="A191" s="0" t="inlineStr">
         <is>
           <t>19229252011</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B191" s="0" t="inlineStr">
         <is>
           <t>2026-04-24 10:36:39</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
+      <c r="C191" s="0" t="inlineStr">
         <is>
           <t>482295</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
+      <c r="D191" s="0" t="inlineStr">
         <is>
           <t>58深绿色</t>
         </is>
       </c>
-      <c r="E191" t="n">
-        <v>0</v>
-      </c>
-      <c r="F191" t="n">
-        <v>0</v>
-      </c>
-      <c r="G191" t="n">
-        <v>1</v>
-      </c>
-      <c r="H191" t="n">
+      <c r="E191" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H191" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="I191" t="n">
-        <v>0</v>
-      </c>
-      <c r="J191" t="n">
-        <v>1</v>
-      </c>
-      <c r="K191" t="n">
-        <v>0</v>
-      </c>
-      <c r="L191" t="n">
-        <v>1</v>
-      </c>
-      <c r="M191" t="n">
-        <v>0</v>
-      </c>
-      <c r="N191" t="n">
-        <v>0</v>
-      </c>
-      <c r="O191" t="inlineStr"/>
+      <c r="I191" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" s="0" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
+      <c r="A192" s="0" t="inlineStr">
         <is>
           <t>19229252011</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B192" s="0" t="inlineStr">
         <is>
           <t>2026-04-24 10:36:39</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
+      <c r="C192" s="0" t="inlineStr">
         <is>
           <t>482295</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
+      <c r="D192" s="0" t="inlineStr">
         <is>
           <t>11粉红色</t>
         </is>
       </c>
-      <c r="E192" t="n">
-        <v>0</v>
-      </c>
-      <c r="F192" t="n">
-        <v>1</v>
-      </c>
-      <c r="G192" t="n">
-        <v>0</v>
-      </c>
-      <c r="H192" t="n">
-        <v>0</v>
-      </c>
-      <c r="I192" t="n">
-        <v>1</v>
-      </c>
-      <c r="J192" t="n">
-        <v>1</v>
-      </c>
-      <c r="K192" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" t="n">
-        <v>0</v>
-      </c>
-      <c r="M192" t="n">
-        <v>0</v>
-      </c>
-      <c r="N192" t="n">
-        <v>0</v>
-      </c>
-      <c r="O192" t="inlineStr"/>
+      <c r="E192" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G192" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J192" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" s="0" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
+      <c r="A193" s="0" t="inlineStr">
         <is>
           <t>19229252011</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B193" s="0" t="inlineStr">
         <is>
           <t>2026-04-24 10:36:39</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
+      <c r="C193" s="0" t="inlineStr">
         <is>
           <t>482295</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
+      <c r="D193" s="0" t="inlineStr">
         <is>
           <t>02浅灰色</t>
         </is>
       </c>
-      <c r="E193" t="n">
-        <v>0</v>
-      </c>
-      <c r="F193" t="n">
-        <v>1</v>
-      </c>
-      <c r="G193" t="n">
-        <v>0</v>
-      </c>
-      <c r="H193" t="n">
-        <v>0</v>
-      </c>
-      <c r="I193" t="n">
-        <v>0</v>
-      </c>
-      <c r="J193" t="n">
-        <v>1</v>
-      </c>
-      <c r="K193" t="n">
-        <v>0</v>
-      </c>
-      <c r="L193" t="n">
-        <v>0</v>
-      </c>
-      <c r="M193" t="n">
-        <v>0</v>
-      </c>
-      <c r="N193" t="n">
-        <v>0</v>
-      </c>
-      <c r="O193" t="inlineStr"/>
+      <c r="E193" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K193" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" s="0" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
+      <c r="A194" s="0" t="inlineStr">
         <is>
           <t>19229252011</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B194" s="0" t="inlineStr">
         <is>
           <t>2026-04-24 10:36:39</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
+      <c r="C194" s="0" t="inlineStr">
         <is>
           <t>482295</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D194" s="0" t="inlineStr">
         <is>
           <t>35浅褐色</t>
         </is>
       </c>
-      <c r="E194" t="n">
-        <v>0</v>
-      </c>
-      <c r="F194" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" t="n">
-        <v>0</v>
-      </c>
-      <c r="H194" t="n">
-        <v>0</v>
-      </c>
-      <c r="I194" t="n">
-        <v>1</v>
-      </c>
-      <c r="J194" t="n">
+      <c r="E194" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K194" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" t="n">
+      <c r="K194" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="M194" t="n">
-        <v>0</v>
-      </c>
-      <c r="N194" t="n">
-        <v>0</v>
-      </c>
-      <c r="O194" t="inlineStr"/>
+      <c r="M194" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" s="0" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
+      <c r="A195" s="0" t="inlineStr">
         <is>
           <t>19229252011</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B195" s="0" t="inlineStr">
         <is>
           <t>2026-04-24 10:36:39</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C195" s="0" t="inlineStr">
         <is>
           <t>482295</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
+      <c r="D195" s="0" t="inlineStr">
         <is>
           <t>69藏青色</t>
         </is>
       </c>
-      <c r="E195" t="n">
-        <v>0</v>
-      </c>
-      <c r="F195" t="n">
-        <v>0</v>
-      </c>
-      <c r="G195" t="n">
-        <v>0</v>
-      </c>
-      <c r="H195" t="n">
-        <v>0</v>
-      </c>
-      <c r="I195" t="n">
-        <v>0</v>
-      </c>
-      <c r="J195" t="n">
-        <v>1</v>
-      </c>
-      <c r="K195" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" t="n">
-        <v>0</v>
-      </c>
-      <c r="M195" t="n">
-        <v>0</v>
-      </c>
-      <c r="N195" t="n">
-        <v>0</v>
-      </c>
-      <c r="O195" t="inlineStr"/>
+      <c r="E195" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K195" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" s="0" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
+      <c r="A196" s="0" t="inlineStr">
         <is>
           <t>19229252011</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr">
+      <c r="B196" s="0" t="inlineStr">
         <is>
           <t>2026-04-24 10:36:39</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
+      <c r="C196" s="0" t="inlineStr">
         <is>
           <t>482295</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
+      <c r="D196" s="0" t="inlineStr">
         <is>
           <t>00白色</t>
         </is>
       </c>
-      <c r="E196" t="n">
-        <v>0</v>
-      </c>
-      <c r="F196" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" t="n">
-        <v>0</v>
-      </c>
-      <c r="H196" t="n">
-        <v>0</v>
-      </c>
-      <c r="I196" t="n">
-        <v>0</v>
-      </c>
-      <c r="J196" t="n">
-        <v>0</v>
-      </c>
-      <c r="K196" t="n">
-        <v>0</v>
-      </c>
-      <c r="L196" t="n">
-        <v>0</v>
-      </c>
-      <c r="M196" t="n">
-        <v>0</v>
-      </c>
-      <c r="N196" t="n">
-        <v>0</v>
-      </c>
-      <c r="O196" t="inlineStr"/>
+      <c r="E196" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" s="0" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
+      <c r="A197" s="0" t="inlineStr">
         <is>
           <t>19229252011</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
+      <c r="B197" s="0" t="inlineStr">
         <is>
           <t>2026-04-24 10:36:39</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
+      <c r="C197" s="0" t="inlineStr">
         <is>
           <t>482295</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
+      <c r="D197" s="0" t="inlineStr">
         <is>
           <t>09黑色</t>
         </is>
       </c>
-      <c r="E197" t="n">
-        <v>0</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" t="n">
-        <v>0</v>
-      </c>
-      <c r="H197" t="n">
-        <v>1</v>
-      </c>
-      <c r="I197" t="n">
-        <v>0</v>
-      </c>
-      <c r="J197" t="n">
-        <v>0</v>
-      </c>
-      <c r="K197" t="n">
-        <v>0</v>
-      </c>
-      <c r="L197" t="n">
-        <v>0</v>
-      </c>
-      <c r="M197" t="n">
-        <v>0</v>
-      </c>
-      <c r="N197" t="n">
-        <v>0</v>
-      </c>
-      <c r="O197" t="inlineStr"/>
+      <c r="E197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" s="0" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>优衣库账号</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>货号</t>
+        </is>
+      </c>
+      <c r="D198" s="4" t="inlineStr">
+        <is>
+          <t>色号</t>
+        </is>
+      </c>
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G198" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="J198" s="4" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t>3XL</t>
+        </is>
+      </c>
+      <c r="L198" s="4" t="inlineStr">
+        <is>
+          <t>4XL</t>
+        </is>
+      </c>
+      <c r="M198" s="4" t="inlineStr">
+        <is>
+          <t>5XL</t>
+        </is>
+      </c>
+      <c r="N198" s="4" t="inlineStr">
+        <is>
+          <t>6XL</t>
+        </is>
+      </c>
+      <c r="O198" s="4" t="inlineStr">
+        <is>
+          <t>查询价格：</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B199" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 08:17:04</t>
+        </is>
+      </c>
+      <c r="C199" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D199" s="0" t="inlineStr">
+        <is>
+          <t>54绿色</t>
+        </is>
+      </c>
+      <c r="E199" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G199" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H199" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I199" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J199" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" s="0" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B200" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 08:17:04</t>
+        </is>
+      </c>
+      <c r="C200" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D200" s="0" t="inlineStr">
+        <is>
+          <t>00白色</t>
+        </is>
+      </c>
+      <c r="E200" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G200" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H200" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="I200" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="J200" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O200" s="0" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B201" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 08:17:04</t>
+        </is>
+      </c>
+      <c r="C201" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D201" s="0" t="inlineStr">
+        <is>
+          <t>60浅蓝色</t>
+        </is>
+      </c>
+      <c r="E201" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G201" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H201" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="I201" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J201" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O201" s="0" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B202" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 08:17:04</t>
+        </is>
+      </c>
+      <c r="C202" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D202" s="0" t="inlineStr">
+        <is>
+          <t>09黑色</t>
+        </is>
+      </c>
+      <c r="E202" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G202" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H202" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I202" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J202" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" s="0" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B203" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 08:17:04</t>
+        </is>
+      </c>
+      <c r="C203" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D203" s="0" t="inlineStr">
+        <is>
+          <t>12桃红色</t>
+        </is>
+      </c>
+      <c r="E203" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G203" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I203" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="J203" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" s="0" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B204" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 08:17:04</t>
+        </is>
+      </c>
+      <c r="C204" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D204" s="0" t="inlineStr">
+        <is>
+          <t>14玛瑙红色</t>
+        </is>
+      </c>
+      <c r="E204" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H204" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I204" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J204" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O204" s="0" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B205" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 08:17:04</t>
+        </is>
+      </c>
+      <c r="C205" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D205" s="0" t="inlineStr">
+        <is>
+          <t>66蓝色</t>
+        </is>
+      </c>
+      <c r="E205" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F205" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I205" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J205" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O205" s="0" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B206" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 08:17:04</t>
+        </is>
+      </c>
+      <c r="C206" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D206" s="0" t="inlineStr">
+        <is>
+          <t>02浅灰色</t>
+        </is>
+      </c>
+      <c r="E206" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F206" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H206" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I206" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O206" s="0" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="inlineStr">
+        <is>
+          <t>优衣库账号</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>货号</t>
+        </is>
+      </c>
+      <c r="D207" s="4" t="inlineStr">
+        <is>
+          <t>色号</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H207" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="J207" s="4" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="K207" s="4" t="inlineStr">
+        <is>
+          <t>3XL</t>
+        </is>
+      </c>
+      <c r="L207" s="4" t="inlineStr">
+        <is>
+          <t>4XL</t>
+        </is>
+      </c>
+      <c r="M207" s="4" t="inlineStr">
+        <is>
+          <t>5XL</t>
+        </is>
+      </c>
+      <c r="N207" s="4" t="inlineStr">
+        <is>
+          <t>6XL</t>
+        </is>
+      </c>
+      <c r="O207" s="4" t="inlineStr">
+        <is>
+          <t>查询价格：</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B208" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:17:41</t>
+        </is>
+      </c>
+      <c r="C208" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D208" s="0" t="inlineStr">
+        <is>
+          <t>54绿色</t>
+        </is>
+      </c>
+      <c r="E208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G208" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H208" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I208" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O208" s="0" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B209" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:17:41</t>
+        </is>
+      </c>
+      <c r="C209" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D209" s="0" t="inlineStr">
+        <is>
+          <t>00白色</t>
+        </is>
+      </c>
+      <c r="E209" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F209" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G209" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H209" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="I209" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="J209" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O209" s="0" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B210" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:17:41</t>
+        </is>
+      </c>
+      <c r="C210" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D210" s="0" t="inlineStr">
+        <is>
+          <t>60浅蓝色</t>
+        </is>
+      </c>
+      <c r="E210" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F210" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G210" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H210" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="I210" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J210" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O210" s="0" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B211" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:17:41</t>
+        </is>
+      </c>
+      <c r="C211" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D211" s="0" t="inlineStr">
+        <is>
+          <t>09黑色</t>
+        </is>
+      </c>
+      <c r="E211" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G211" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H211" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I211" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J211" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" s="0" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B212" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:17:41</t>
+        </is>
+      </c>
+      <c r="C212" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D212" s="0" t="inlineStr">
+        <is>
+          <t>12桃红色</t>
+        </is>
+      </c>
+      <c r="E212" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F212" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G212" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I212" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="J212" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" s="0" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B213" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:17:41</t>
+        </is>
+      </c>
+      <c r="C213" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D213" s="0" t="inlineStr">
+        <is>
+          <t>14玛瑙红色</t>
+        </is>
+      </c>
+      <c r="E213" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F213" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G213" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H213" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I213" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J213" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" s="0" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B214" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:17:41</t>
+        </is>
+      </c>
+      <c r="C214" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D214" s="0" t="inlineStr">
+        <is>
+          <t>66蓝色</t>
+        </is>
+      </c>
+      <c r="E214" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F214" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I214" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J214" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" s="0" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B215" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:17:41</t>
+        </is>
+      </c>
+      <c r="C215" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D215" s="0" t="inlineStr">
+        <is>
+          <t>02浅灰色</t>
+        </is>
+      </c>
+      <c r="E215" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F215" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H215" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I215" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O215" s="0" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>优衣库账号</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>货号</t>
+        </is>
+      </c>
+      <c r="D216" s="4" t="inlineStr">
+        <is>
+          <t>色号</t>
+        </is>
+      </c>
+      <c r="E216" s="4" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F216" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G216" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H216" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="J216" s="4" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="K216" s="4" t="inlineStr">
+        <is>
+          <t>3XL</t>
+        </is>
+      </c>
+      <c r="L216" s="4" t="inlineStr">
+        <is>
+          <t>4XL</t>
+        </is>
+      </c>
+      <c r="M216" s="4" t="inlineStr">
+        <is>
+          <t>5XL</t>
+        </is>
+      </c>
+      <c r="N216" s="4" t="inlineStr">
+        <is>
+          <t>6XL</t>
+        </is>
+      </c>
+      <c r="O216" s="4" t="inlineStr">
+        <is>
+          <t>查询价格：199</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B217" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:28:11</t>
+        </is>
+      </c>
+      <c r="C217" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D217" s="0" t="inlineStr">
+        <is>
+          <t>54绿色</t>
+        </is>
+      </c>
+      <c r="E217" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I217" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J217" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" s="0" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B218" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:28:11</t>
+        </is>
+      </c>
+      <c r="C218" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D218" s="0" t="inlineStr">
+        <is>
+          <t>00白色</t>
+        </is>
+      </c>
+      <c r="E218" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H218" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="J218" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" s="0" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B219" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:28:11</t>
+        </is>
+      </c>
+      <c r="C219" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D219" s="0" t="inlineStr">
+        <is>
+          <t>60浅蓝色</t>
+        </is>
+      </c>
+      <c r="E219" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F219" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G219" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="I219" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J219" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O219" s="0" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B220" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:28:11</t>
+        </is>
+      </c>
+      <c r="C220" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D220" s="0" t="inlineStr">
+        <is>
+          <t>09黑色</t>
+        </is>
+      </c>
+      <c r="E220" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G220" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H220" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J220" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O220" s="0" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B221" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:28:11</t>
+        </is>
+      </c>
+      <c r="C221" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D221" s="0" t="inlineStr">
+        <is>
+          <t>12桃红色</t>
+        </is>
+      </c>
+      <c r="E221" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G221" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I221" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="J221" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O221" s="0" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B222" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:28:11</t>
+        </is>
+      </c>
+      <c r="C222" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D222" s="0" t="inlineStr">
+        <is>
+          <t>14玛瑙红色</t>
+        </is>
+      </c>
+      <c r="E222" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F222" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H222" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I222" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J222" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" s="0" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B223" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:28:11</t>
+        </is>
+      </c>
+      <c r="C223" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D223" s="0" t="inlineStr">
+        <is>
+          <t>66蓝色</t>
+        </is>
+      </c>
+      <c r="E223" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F223" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I223" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J223" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" s="0" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B224" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 11:28:11</t>
+        </is>
+      </c>
+      <c r="C224" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D224" s="0" t="inlineStr">
+        <is>
+          <t>02浅灰色</t>
+        </is>
+      </c>
+      <c r="E224" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F224" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H224" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I224" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" s="0" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>优衣库账号</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>货号</t>
+        </is>
+      </c>
+      <c r="D225" s="4" t="inlineStr">
+        <is>
+          <t>色号</t>
+        </is>
+      </c>
+      <c r="E225" s="4" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F225" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G225" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H225" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="J225" s="4" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="K225" s="4" t="inlineStr">
+        <is>
+          <t>3XL</t>
+        </is>
+      </c>
+      <c r="L225" s="4" t="inlineStr">
+        <is>
+          <t>4XL</t>
+        </is>
+      </c>
+      <c r="M225" s="4" t="inlineStr">
+        <is>
+          <t>5XL</t>
+        </is>
+      </c>
+      <c r="N225" s="4" t="inlineStr">
+        <is>
+          <t>6XL</t>
+        </is>
+      </c>
+      <c r="O225" s="4" t="inlineStr">
+        <is>
+          <t>查询价格：</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B226" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:15:01</t>
+        </is>
+      </c>
+      <c r="C226" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D226" s="0" t="inlineStr">
+        <is>
+          <t>54绿色</t>
+        </is>
+      </c>
+      <c r="E226" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F226" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G226" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I226" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J226" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" s="0" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B227" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:15:01</t>
+        </is>
+      </c>
+      <c r="C227" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D227" s="0" t="inlineStr">
+        <is>
+          <t>00白色</t>
+        </is>
+      </c>
+      <c r="E227" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F227" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G227" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H227" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="I227" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="J227" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" s="0" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B228" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:15:01</t>
+        </is>
+      </c>
+      <c r="C228" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D228" s="0" t="inlineStr">
+        <is>
+          <t>60浅蓝色</t>
+        </is>
+      </c>
+      <c r="E228" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F228" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G228" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H228" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="I228" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J228" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" s="0" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B229" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:15:01</t>
+        </is>
+      </c>
+      <c r="C229" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D229" s="0" t="inlineStr">
+        <is>
+          <t>09黑色</t>
+        </is>
+      </c>
+      <c r="E229" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F229" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G229" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H229" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I229" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J229" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N229" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O229" s="0" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B230" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:15:01</t>
+        </is>
+      </c>
+      <c r="C230" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D230" s="0" t="inlineStr">
+        <is>
+          <t>12桃红色</t>
+        </is>
+      </c>
+      <c r="E230" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G230" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I230" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="J230" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O230" s="0" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B231" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:15:01</t>
+        </is>
+      </c>
+      <c r="C231" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D231" s="0" t="inlineStr">
+        <is>
+          <t>14玛瑙红色</t>
+        </is>
+      </c>
+      <c r="E231" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F231" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H231" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I231" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J231" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N231" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O231" s="0" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B232" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:15:01</t>
+        </is>
+      </c>
+      <c r="C232" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D232" s="0" t="inlineStr">
+        <is>
+          <t>66蓝色</t>
+        </is>
+      </c>
+      <c r="E232" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F232" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G232" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I232" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J232" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M232" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N232" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" s="0" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B233" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:15:01</t>
+        </is>
+      </c>
+      <c r="C233" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D233" s="0" t="inlineStr">
+        <is>
+          <t>02浅灰色</t>
+        </is>
+      </c>
+      <c r="E233" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F233" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H233" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I233" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N233" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O233" s="0" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
+        <is>
+          <t>优衣库账号</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>货号</t>
+        </is>
+      </c>
+      <c r="D234" s="4" t="inlineStr">
+        <is>
+          <t>色号</t>
+        </is>
+      </c>
+      <c r="E234" s="4" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F234" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G234" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H234" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="J234" s="4" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="K234" s="4" t="inlineStr">
+        <is>
+          <t>3XL</t>
+        </is>
+      </c>
+      <c r="L234" s="4" t="inlineStr">
+        <is>
+          <t>4XL</t>
+        </is>
+      </c>
+      <c r="M234" s="4" t="inlineStr">
+        <is>
+          <t>5XL</t>
+        </is>
+      </c>
+      <c r="N234" s="4" t="inlineStr">
+        <is>
+          <t>6XL</t>
+        </is>
+      </c>
+      <c r="O234" s="4" t="inlineStr">
+        <is>
+          <t>查询价格：</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B235" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C235" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D235" s="0" t="inlineStr">
+        <is>
+          <t>54绿色</t>
+        </is>
+      </c>
+      <c r="E235" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F235" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G235" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="H235" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I235" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J235" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M235" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N235" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" s="0" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B236" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C236" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D236" s="0" t="inlineStr">
+        <is>
+          <t>00白色</t>
+        </is>
+      </c>
+      <c r="E236" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F236" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G236" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H236" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="I236" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="J236" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N236" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" s="0" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B237" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C237" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D237" s="0" t="inlineStr">
+        <is>
+          <t>60浅蓝色</t>
+        </is>
+      </c>
+      <c r="E237" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F237" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G237" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="H237" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="I237" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J237" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M237" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N237" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O237" s="0" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B238" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C238" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D238" s="0" t="inlineStr">
+        <is>
+          <t>09黑色</t>
+        </is>
+      </c>
+      <c r="E238" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F238" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G238" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H238" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I238" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J238" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N238" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O238" s="0" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B239" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C239" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D239" s="0" t="inlineStr">
+        <is>
+          <t>12桃红色</t>
+        </is>
+      </c>
+      <c r="E239" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F239" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G239" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I239" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="J239" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O239" s="0" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B240" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C240" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D240" s="0" t="inlineStr">
+        <is>
+          <t>14玛瑙红色</t>
+        </is>
+      </c>
+      <c r="E240" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F240" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H240" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I240" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J240" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M240" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N240" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O240" s="0" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B241" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C241" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D241" s="0" t="inlineStr">
+        <is>
+          <t>66蓝色</t>
+        </is>
+      </c>
+      <c r="E241" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F241" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G241" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I241" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J241" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M241" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N241" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" s="0" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B242" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C242" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D242" s="0" t="inlineStr">
+        <is>
+          <t>02浅灰色</t>
+        </is>
+      </c>
+      <c r="E242" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F242" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G242" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H242" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I242" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M242" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N242" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O242" s="0" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
+        <is>
+          <t>优衣库账号</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>货号</t>
+        </is>
+      </c>
+      <c r="D243" s="4" t="inlineStr">
+        <is>
+          <t>色号</t>
+        </is>
+      </c>
+      <c r="E243" s="4" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G243" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H243" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I243" s="4" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="J243" s="4" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="K243" s="4" t="inlineStr">
+        <is>
+          <t>3XL</t>
+        </is>
+      </c>
+      <c r="L243" s="4" t="inlineStr">
+        <is>
+          <t>4XL</t>
+        </is>
+      </c>
+      <c r="M243" s="4" t="inlineStr">
+        <is>
+          <t>5XL</t>
+        </is>
+      </c>
+      <c r="N243" s="4" t="inlineStr">
+        <is>
+          <t>6XL</t>
+        </is>
+      </c>
+      <c r="O243" s="4" t="inlineStr">
+        <is>
+          <t>查询价格：199</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B244" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C244" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D244" s="0" t="inlineStr">
+        <is>
+          <t>54绿色</t>
+        </is>
+      </c>
+      <c r="E244" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F244" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G244" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I244" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J244" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L244" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M244" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" s="0" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B245" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C245" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D245" s="0" t="inlineStr">
+        <is>
+          <t>00白色</t>
+        </is>
+      </c>
+      <c r="E245" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F245" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="H245" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I245" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="J245" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M245" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N245" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" s="0" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B246" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C246" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D246" s="0" t="inlineStr">
+        <is>
+          <t>60浅蓝色</t>
+        </is>
+      </c>
+      <c r="E246" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F246" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G246" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="I246" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J246" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L246" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M246" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N246" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O246" s="0" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B247" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C247" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D247" s="0" t="inlineStr">
+        <is>
+          <t>09黑色</t>
+        </is>
+      </c>
+      <c r="E247" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G247" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H247" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I247" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J247" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L247" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M247" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N247" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O247" s="0" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B248" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C248" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D248" s="0" t="inlineStr">
+        <is>
+          <t>12桃红色</t>
+        </is>
+      </c>
+      <c r="E248" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F248" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G248" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I248" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="J248" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L248" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M248" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N248" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O248" s="0" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B249" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C249" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D249" s="0" t="inlineStr">
+        <is>
+          <t>14玛瑙红色</t>
+        </is>
+      </c>
+      <c r="E249" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F249" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G249" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="H249" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="I249" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J249" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L249" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M249" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N249" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O249" s="0" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B250" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C250" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D250" s="0" t="inlineStr">
+        <is>
+          <t>66蓝色</t>
+        </is>
+      </c>
+      <c r="E250" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F250" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I250" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J250" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L250" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M250" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N250" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O250" s="0" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B251" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:17:43</t>
+        </is>
+      </c>
+      <c r="C251" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D251" s="0" t="inlineStr">
+        <is>
+          <t>02浅灰色</t>
+        </is>
+      </c>
+      <c r="E251" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F251" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G251" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H251" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I251" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L251" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M251" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N251" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O251" s="0" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>优衣库账号</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>货号</t>
+        </is>
+      </c>
+      <c r="D252" s="4" t="inlineStr">
+        <is>
+          <t>色号</t>
+        </is>
+      </c>
+      <c r="E252" s="4" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F252" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G252" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H252" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I252" s="4" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="J252" s="4" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="K252" s="4" t="inlineStr">
+        <is>
+          <t>3XL</t>
+        </is>
+      </c>
+      <c r="L252" s="4" t="inlineStr">
+        <is>
+          <t>4XL</t>
+        </is>
+      </c>
+      <c r="M252" s="4" t="inlineStr">
+        <is>
+          <t>5XL</t>
+        </is>
+      </c>
+      <c r="N252" s="4" t="inlineStr">
+        <is>
+          <t>6XL</t>
+        </is>
+      </c>
+      <c r="O252" s="4" t="inlineStr">
+        <is>
+          <t>查询价格：</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B253" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C253" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D253" s="0" t="inlineStr">
+        <is>
+          <t>54绿色</t>
+        </is>
+      </c>
+      <c r="E253" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F253" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G253" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="H253" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="I253" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J253" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L253" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M253" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N253" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O253" s="0" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B254" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C254" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D254" s="0" t="inlineStr">
+        <is>
+          <t>00白色</t>
+        </is>
+      </c>
+      <c r="E254" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F254" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="G254" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H254" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="I254" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="J254" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M254" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N254" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O254" s="0" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B255" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C255" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D255" s="0" t="inlineStr">
+        <is>
+          <t>60浅蓝色</t>
+        </is>
+      </c>
+      <c r="E255" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F255" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="G255" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="H255" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="I255" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="J255" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L255" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M255" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N255" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O255" s="0" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B256" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C256" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D256" s="0" t="inlineStr">
+        <is>
+          <t>09黑色</t>
+        </is>
+      </c>
+      <c r="E256" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F256" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G256" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H256" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="I256" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="J256" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M256" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N256" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" s="0" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B257" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C257" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D257" s="0" t="inlineStr">
+        <is>
+          <t>12桃红色</t>
+        </is>
+      </c>
+      <c r="E257" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F257" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G257" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H257" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I257" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="J257" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M257" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N257" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O257" s="0" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B258" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C258" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D258" s="0" t="inlineStr">
+        <is>
+          <t>14玛瑙红色</t>
+        </is>
+      </c>
+      <c r="E258" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="H258" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="I258" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="J258" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M258" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N258" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" s="0" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B259" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C259" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D259" s="0" t="inlineStr">
+        <is>
+          <t>66蓝色</t>
+        </is>
+      </c>
+      <c r="E259" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F259" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G259" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I259" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J259" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M259" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N259" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" s="0" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="0" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B260" s="0" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C260" s="0" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D260" s="0" t="inlineStr">
+        <is>
+          <t>02浅灰色</t>
+        </is>
+      </c>
+      <c r="E260" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F260" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G260" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="H260" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I260" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L260" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M260" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N260" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O260" s="0" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>优衣库账号</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>货号</t>
+        </is>
+      </c>
+      <c r="D261" s="4" t="inlineStr">
+        <is>
+          <t>色号</t>
+        </is>
+      </c>
+      <c r="E261" s="4" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="F261" s="4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G261" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H261" s="4" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="J261" s="4" t="inlineStr">
+        <is>
+          <t>2XL</t>
+        </is>
+      </c>
+      <c r="K261" s="4" t="inlineStr">
+        <is>
+          <t>3XL</t>
+        </is>
+      </c>
+      <c r="L261" s="4" t="inlineStr">
+        <is>
+          <t>4XL</t>
+        </is>
+      </c>
+      <c r="M261" s="4" t="inlineStr">
+        <is>
+          <t>5XL</t>
+        </is>
+      </c>
+      <c r="N261" s="4" t="inlineStr">
+        <is>
+          <t>6XL</t>
+        </is>
+      </c>
+      <c r="O261" s="4" t="inlineStr">
+        <is>
+          <t>查询价格：199</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>54绿色</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="n">
+        <v>3</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="n">
+        <v>3</v>
+      </c>
+      <c r="I262" t="n">
+        <v>3</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" t="n">
+        <v>0</v>
+      </c>
+      <c r="M262" t="n">
+        <v>0</v>
+      </c>
+      <c r="N262" t="n">
+        <v>0</v>
+      </c>
+      <c r="O262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>00白色</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>0</v>
+      </c>
+      <c r="F263" t="n">
+        <v>6</v>
+      </c>
+      <c r="G263" t="n">
+        <v>10</v>
+      </c>
+      <c r="H263" t="n">
+        <v>8</v>
+      </c>
+      <c r="I263" t="n">
+        <v>7</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="n">
+        <v>0</v>
+      </c>
+      <c r="L263" t="n">
+        <v>0</v>
+      </c>
+      <c r="M263" t="n">
+        <v>0</v>
+      </c>
+      <c r="N263" t="n">
+        <v>0</v>
+      </c>
+      <c r="O263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>60浅蓝色</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>0</v>
+      </c>
+      <c r="F264" t="n">
+        <v>5</v>
+      </c>
+      <c r="G264" t="n">
+        <v>5</v>
+      </c>
+      <c r="H264" t="n">
+        <v>14</v>
+      </c>
+      <c r="I264" t="n">
+        <v>9</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" t="n">
+        <v>0</v>
+      </c>
+      <c r="M264" t="n">
+        <v>0</v>
+      </c>
+      <c r="N264" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>09黑色</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+      <c r="F265" t="n">
+        <v>4</v>
+      </c>
+      <c r="G265" t="n">
+        <v>5</v>
+      </c>
+      <c r="H265" t="n">
+        <v>5</v>
+      </c>
+      <c r="I265" t="n">
+        <v>4</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" t="n">
+        <v>0</v>
+      </c>
+      <c r="M265" t="n">
+        <v>0</v>
+      </c>
+      <c r="N265" t="n">
+        <v>0</v>
+      </c>
+      <c r="O265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>12桃红色</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+      <c r="F266" t="n">
+        <v>3</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>4</v>
+      </c>
+      <c r="I266" t="n">
+        <v>8</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" t="n">
+        <v>0</v>
+      </c>
+      <c r="N266" t="n">
+        <v>0</v>
+      </c>
+      <c r="O266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>14玛瑙红色</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" t="n">
+        <v>0</v>
+      </c>
+      <c r="G267" t="n">
+        <v>5</v>
+      </c>
+      <c r="H267" t="n">
+        <v>2</v>
+      </c>
+      <c r="I267" t="n">
+        <v>5</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="n">
+        <v>0</v>
+      </c>
+      <c r="L267" t="n">
+        <v>0</v>
+      </c>
+      <c r="M267" t="n">
+        <v>0</v>
+      </c>
+      <c r="N267" t="n">
+        <v>0</v>
+      </c>
+      <c r="O267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>66蓝色</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" t="n">
+        <v>4</v>
+      </c>
+      <c r="I268" t="n">
+        <v>3</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L268" t="n">
+        <v>0</v>
+      </c>
+      <c r="M268" t="n">
+        <v>0</v>
+      </c>
+      <c r="N268" t="n">
+        <v>0</v>
+      </c>
+      <c r="O268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>17015859679</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-05-18 12:34:39</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>483281</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>02浅灰色</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
+      <c r="F269" t="n">
+        <v>0</v>
+      </c>
+      <c r="G269" t="n">
+        <v>3</v>
+      </c>
+      <c r="H269" t="n">
+        <v>4</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L269" t="n">
+        <v>0</v>
+      </c>
+      <c r="M269" t="n">
+        <v>0</v>
+      </c>
+      <c r="N269" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
